--- a/Golden Cala/Scripts/Shoof Integration/Transfer Module/Transfer Order/Technical Reference.xlsx
+++ b/Golden Cala/Scripts/Shoof Integration/Transfer Module/Transfer Order/Technical Reference.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NetSuiteCompanies\Golden Cala\Scripts\Shoof Integration\Transfer Module\Transfer Order\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD775E9B-CB4D-4D87-BBBB-8424AB80D721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BFBC34-039B-440E-B345-60828AB2363E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9045" yWindow="2355" windowWidth="17280" windowHeight="8925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -441,7 +441,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
